--- a/Дело3а-78-2026Таганай/03_Учредительные/00_Ведомость_03_Учредительные_документы.xlsx
+++ b/Дело3а-78-2026Таганай/03_Учредительные/00_Ведомость_03_Учредительные_документы.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость 03" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 03'!$B$11:$H$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ведомость 03'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,9 +20,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,23 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0001696F"/>
+      <i val="1"/>
+      <color rgb="00A12C7B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="007A7974"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -107,7 +96,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -118,18 +107,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0001696F"/>
         <bgColor rgb="0001696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F1E3"/>
-        <bgColor rgb="00E8F1E3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4EC"/>
-        <bgColor rgb="00E8F4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,30 +153,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H20"/>
+  <dimension ref="B2:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -613,7 +570,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -622,11 +579,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>7 КБ</t>
+          <t>0 КБ</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.92958244933</v>
+        <v>46158.29716852435</v>
       </c>
     </row>
     <row r="9">
@@ -679,85 +636,61 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
+    <row r="12">
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>03.1</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Сводная ведомость</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Сводная_ведомость.xlsx</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>46157.92520833189</v>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>7 КБ</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+          <t>В этой папке пока нет элементов верхнего уровня. Добавьте файлы и запустите скрипт повторно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Подсказки:</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Подсказки:</t>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>• Перезапуск скрипта перезапишет файл (в т.ч. наименования).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B11:H12"/>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B14:H14"/>
     <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B15:H15"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Дело3а-78-2026Таганай/03_Учредительные/00_Ведомость_03_Учредительные_документы.xlsx
+++ b/Дело3а-78-2026Таганай/03_Учредительные/00_Ведомость_03_Учредительные_документы.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46158.29716852435</v>
+        <v>46158.37372865013</v>
       </c>
     </row>
     <row r="9">
